--- a/It23225138_Test cases.xlsx
+++ b/It23225138_Test cases.xlsx
@@ -853,14 +853,10 @@
           <t>මේ assignment එක කරන්න පොඩ්ඩක් අමාරුයි බං.</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>මේ assignment එක කරන්න පොඩ්ඩක් අමාරුයි වගේ.</t>
-        </is>
-      </c>
+      <c r="E15" s="6" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UI Error</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>

--- a/It23225138_Test cases.xlsx
+++ b/It23225138_Test cases.xlsx
@@ -881,14 +881,10 @@
           <t>මට මේක තේරෙන්නේම නැ.</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>මට මේක තේරෙන්නෙම නෑ.</t>
-        </is>
-      </c>
+      <c r="E16" s="6" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UI Error</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>

--- a/It23225138_Test cases.xlsx
+++ b/It23225138_Test cases.xlsx
@@ -909,14 +909,10 @@
           <t>ඒ lecturer කිව්ව එක හරියට අහුවේ නැද්ද?</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>ඒ lecturer කිව්වා ඒක හරියට ඇහුවේ නැද්ද?</t>
-        </is>
-      </c>
+      <c r="E17" s="6" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UI Error</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
